--- a/docs/downloads/04/tbl_other_write_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_write_sex_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -424,7 +424,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1090,7 +1090,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1136,7 +1136,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1205,7 +1205,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1274,7 +1274,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1366,7 +1366,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1412,7 +1412,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1481,7 +1481,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1504,7 +1504,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1527,7 +1527,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
